--- a/Data/exogenous_data/Finland_MASTER_Calibration_old_UPDATED.xlsx
+++ b/Data/exogenous_data/Finland_MASTER_Calibration_old_UPDATED.xlsx
@@ -6468,7 +6468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" style="11" min="1" max="1"/>
@@ -6878,6 +6878,33 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>Priority-ranked calibration fixes based on model vs reality gaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Copilot</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nuclear thermal efficiency corrected: URANIUM ratio -2.7027 → -3.125 (37% → 32%)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Data/2017/00_INDEP/Layers_in_out.csv (NUCLEAR + NUCLEAR_SMR rows)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Finnish plants (Loviisa PWR + Olkiluoto BWR, 1970s-80s vintage) operate at ~32%. Fixes PE_nuclear underestimation (56 → ~65 TWh). Also applied to NUCLEAR_SMR for consistency.</t>
         </is>
       </c>
     </row>
@@ -11936,6 +11963,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -11980,7 +12008,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-2.7027</v>
+        <v>-3.125</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -11988,7 +12016,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="n"/>
     </row>

--- a/Data/exogenous_data/Finland_MASTER_Calibration_old_UPDATED.xlsx
+++ b/Data/exogenous_data/Finland_MASTER_Calibration_old_UPDATED.xlsx
@@ -6468,7 +6468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="12" customWidth="1" style="11" min="1" max="1"/>
@@ -6905,6 +6905,87 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>Finnish plants (Loviisa PWR + Olkiluoto BWR, 1970s-80s vintage) operate at ~32%. Fixes PE_nuclear underestimation (56 → ~65 TWh). Also applied to NUCLEAR_SMR for consistency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Copilot</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FIXED loss_network ELECTRICITY: 0.0864 → 0.03 (EU avg → Finnish value 3%). FIXED loss_network HEAT_LOW_T_DHN: 0.05 → 0.085 (EU avg → Finnish value 8.5%).</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Data/2017/00_INDEP/Misc_indep.json</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Both values were documented as wrong in 07_Global_Parameters (OVERESTIMATED/UNDERESTIMATED). loss_network is INDEP (not per-region in AMPL), safe to fix for single-country FI run. Impact: -3,693 GWh excess ELEC losses; +1,844 GWh correct DHN losses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Copilot</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Demand boundary correction (Stats FI vs JRC-IDEES): IND ELECTRICITY 23424.87-&gt;44524.87 GWh (+21100); IND HEAT_HIGH_T 59820.73-&gt;38720.73 GWh (-21100). Total IND energy conserved at 83245.60 GWh.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Data/2017/FI/Demands.csv</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JRC-IDEES classifies Finnish pulp/paper/steel motor+process electricity as HEAT_HIGH_T (end-use boundary). Stats Finland records it as ELECTRICITY (commodity-flow). Corrected to Stats FI boundary to fix ~11 TWh import gap. See Docs/finland2017_demand_boundary_audit.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Copilot</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IND_BOILER f_min scaled to new HEAT_HIGH_T (factor 0.647=38720/59820): IND_BOILER_WOOD 5.0-&gt;3.2 GW; IND_BOILER_COAL 0.5-&gt;0.3 GW.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Data/2017/FI/Technologies.csv</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Old IND_BOILER_WOOD f_min=5.0 GW would exceed new HEAT_HIGH_T avg capacity 4.42 GW. Proportionally scaled to avoid infeasibility.</t>
         </is>
       </c>
     </row>
@@ -7873,13 +7954,13 @@
         <v>10822.33</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>23424.87</v>
+        <v>44524.87</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>43007.31</v>
+        <v>64107.31</v>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
@@ -7910,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>59820.73</v>
+        <v>38720.73</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>59820.73</v>
+        <v>38720.73</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
@@ -11699,7 +11780,7 @@
     <row r="1" ht="18" customHeight="1" s="11">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Global Parameters (00_INDEP) — Not Overrideable per Country</t>
+          <t>Global Parameters (00_INDEP) — Finland-specific values applied for single-country run</t>
         </is>
       </c>
     </row>
@@ -11766,16 +11847,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0864</v>
+        <v>0.03</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>8.64% grid losses (EU average)</t>
+          <t>3% grid losses (Finnish Energy) — FIXED from 0.0864 EU average</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>~3% (Finnish Energy) — OVERESTIMATED</t>
+          <t>~3% (Finnish Energy) — CORRECTED (was OVERESTIMATED at 8.64%)</t>
         </is>
       </c>
     </row>
@@ -11786,16 +11867,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.05</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>5% DH losses (EU average)</t>
+          <t>8.5% DH losses (Finnish Energy) — FIXED from 0.05 EU average</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>~8.5% (Finnish Energy) — UNDERESTIMATED</t>
+          <t>~8.5% (Finnish Energy) — CORRECTED (was UNDERESTIMATED at 5%)</t>
         </is>
       </c>
     </row>
@@ -11963,7 +12044,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
